--- a/Detalle_comisiones/flujocomisiones.xlsx
+++ b/Detalle_comisiones/flujocomisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdiseguroscom-my.sharepoint.com/personal/wilson_jerez_hdiseguros_com_co/Documents/Documentos/hdi-extract-sql-to-knime/Detalle_comisiones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_F25DC773A252ABDACC104869F9DA44D65BDE58FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90BE1A8E-42A6-4E86-919B-9DD9C7E1D930}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC104869F9DA44D65BDE58FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B46A78A-53AC-4F7C-B9EB-FD8197BE8EEF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,6 +566,7 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="44.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
